--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7DC3E2-F365-4585-9260-E52BFAFBEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DDE845-7EA1-4A6F-96D6-08001D2228FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5158,7 +5158,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789F7666-2F89-4528-B8C6-CE4932FDFD97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2360CA8B-2E02-48C0-8B23-22CD49E97916}">
   <dimension ref="B3:I46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6291,7 +6291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D657477-3E44-4872-B620-16FB977A2F9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD71109-EC8B-41A9-ADED-C4668F470CC4}">
   <dimension ref="B3:I46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DDE845-7EA1-4A6F-96D6-08001D2228FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A03646-1329-4AC7-A198-859925A55F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5158,7 +5158,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2360CA8B-2E02-48C0-8B23-22CD49E97916}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A310382-D434-46D7-B971-F7E6EB12528A}">
   <dimension ref="B3:I46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6291,7 +6291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD71109-EC8B-41A9-ADED-C4668F470CC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3099DD4A-8C6D-4EF4-A088-AE4031F7C23F}">
   <dimension ref="B3:I46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A03646-1329-4AC7-A198-859925A55F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0B4E37-E48F-4CBE-B111-F24E7BD77522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3021" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3069" uniqueCount="920">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -2292,18 +2292,18 @@
     <t>grid node -- way/169794711-220 (Bendigo, 229 km)</t>
   </si>
   <si>
-    <t>e_Blackwall_AUS</t>
-  </si>
-  <si>
-    <t>grid node -- way/170832455-275 (Brisbane, 25 km)</t>
-  </si>
-  <si>
     <t>e_Bouldercombe_AUS</t>
   </si>
   <si>
     <t>grid node -- way/171486427-275 (Rockhampton, 18 km)</t>
   </si>
   <si>
+    <t>e_Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>grid node -- way/172587651-275 (Brisbane, 30 km)</t>
+  </si>
+  <si>
     <t>e_Broadsound_AUS</t>
   </si>
   <si>
@@ -2364,6 +2364,12 @@
     <t>grid node -- way/164764363-275 (Adelaide, 276 km)</t>
   </si>
   <si>
+    <t>e_Dubbo_AUS</t>
+  </si>
+  <si>
+    <t>grid node -- way/169406848-330 (Central Coast, 226 km)</t>
+  </si>
+  <si>
     <t>e_GinGin_AUS</t>
   </si>
   <si>
@@ -2400,6 +2406,12 @@
     <t>grid node -- way/223939702-220 (Perth, 229 km)</t>
   </si>
   <si>
+    <t>e_Morawa_AUS</t>
+  </si>
+  <si>
+    <t>grid node -- way/583513574-330 (Perth, 320 km)</t>
+  </si>
+  <si>
     <t>e_MountPiper_AUS</t>
   </si>
   <si>
@@ -2436,6 +2448,12 @@
     <t>grid node -- AU57-330 (Perth, 26 km)</t>
   </si>
   <si>
+    <t>e_PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>grid node -- AU3-220 (Perth, 1309 km)</t>
+  </si>
+  <si>
     <t>e_Robertstown_AUS</t>
   </si>
   <si>
@@ -2544,18 +2562,18 @@
     <t>heat at grid node -- way/169794711-220 (Bendigo, 229 km)</t>
   </si>
   <si>
-    <t>h_Blackwall_AUS</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170832455-275 (Brisbane, 25 km)</t>
-  </si>
-  <si>
     <t>h_Bouldercombe_AUS</t>
   </si>
   <si>
     <t>heat at grid node -- way/171486427-275 (Rockhampton, 18 km)</t>
   </si>
   <si>
+    <t>h_Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/172587651-275 (Brisbane, 30 km)</t>
+  </si>
+  <si>
     <t>h_Broadsound_AUS</t>
   </si>
   <si>
@@ -2616,6 +2634,12 @@
     <t>heat at grid node -- way/164764363-275 (Adelaide, 276 km)</t>
   </si>
   <si>
+    <t>h_Dubbo_AUS</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/169406848-330 (Central Coast, 226 km)</t>
+  </si>
+  <si>
     <t>h_GinGin_AUS</t>
   </si>
   <si>
@@ -2652,6 +2676,12 @@
     <t>heat at grid node -- way/223939702-220 (Perth, 229 km)</t>
   </si>
   <si>
+    <t>h_Morawa_AUS</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/583513574-330 (Perth, 320 km)</t>
+  </si>
+  <si>
     <t>h_MountPiper_AUS</t>
   </si>
   <si>
@@ -2686,6 +2716,12 @@
   </si>
   <si>
     <t>heat at grid node -- AU57-330 (Perth, 26 km)</t>
+  </si>
+  <si>
+    <t>h_PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>heat at grid node -- AU3-220 (Perth, 1309 km)</t>
   </si>
   <si>
     <t>h_Robertstown_AUS</t>
@@ -5158,8 +5194,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A310382-D434-46D7-B971-F7E6EB12528A}">
-  <dimension ref="B3:I46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE47005-90C5-46FF-AE6E-BECFAB6521D8}">
+  <dimension ref="B3:I49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -5198,13 +5234,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -5224,13 +5260,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -5250,13 +5286,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -5276,13 +5312,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -5302,13 +5338,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -5328,13 +5364,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -5354,13 +5390,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -5380,13 +5416,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -5406,13 +5442,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -5432,13 +5468,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -5458,13 +5494,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -5484,13 +5520,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -5510,13 +5546,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -5536,13 +5572,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -5562,13 +5598,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -5588,13 +5624,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -5614,13 +5650,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -5640,13 +5676,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -5666,13 +5702,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -5692,13 +5728,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -5718,13 +5754,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -5744,13 +5780,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -5770,13 +5806,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -5796,13 +5832,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -5822,13 +5858,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -5848,13 +5884,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -5874,13 +5910,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -5900,13 +5936,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -5926,13 +5962,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -5952,13 +5988,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -5978,13 +6014,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -6004,13 +6040,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -6030,13 +6066,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -6056,13 +6092,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -6082,13 +6118,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -6108,13 +6144,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -6134,13 +6170,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -6160,13 +6196,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -6186,13 +6222,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -6212,13 +6248,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -6238,13 +6274,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -6264,13 +6300,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -6282,6 +6318,84 @@
         <v>741</v>
       </c>
       <c r="I46" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>914</v>
+      </c>
+      <c r="D47" t="s">
+        <v>243</v>
+      </c>
+      <c r="E47" t="s">
+        <v>915</v>
+      </c>
+      <c r="F47" t="s">
+        <v>233</v>
+      </c>
+      <c r="G47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H47" t="s">
+        <v>741</v>
+      </c>
+      <c r="I47" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>916</v>
+      </c>
+      <c r="D48" t="s">
+        <v>243</v>
+      </c>
+      <c r="E48" t="s">
+        <v>917</v>
+      </c>
+      <c r="F48" t="s">
+        <v>233</v>
+      </c>
+      <c r="G48" t="s">
+        <v>232</v>
+      </c>
+      <c r="H48" t="s">
+        <v>741</v>
+      </c>
+      <c r="I48" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>918</v>
+      </c>
+      <c r="D49" t="s">
+        <v>243</v>
+      </c>
+      <c r="E49" t="s">
+        <v>919</v>
+      </c>
+      <c r="F49" t="s">
+        <v>233</v>
+      </c>
+      <c r="G49" t="s">
+        <v>232</v>
+      </c>
+      <c r="H49" t="s">
+        <v>741</v>
+      </c>
+      <c r="I49" t="s">
         <v>247</v>
       </c>
     </row>
@@ -6291,8 +6405,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3099DD4A-8C6D-4EF4-A088-AE4031F7C23F}">
-  <dimension ref="B3:I46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1D028D5-41AD-4C92-A7FC-A5B3AE889C18}">
+  <dimension ref="B3:I49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -7415,6 +7529,84 @@
         <v>741</v>
       </c>
       <c r="I46" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>824</v>
+      </c>
+      <c r="D47" t="s">
+        <v>243</v>
+      </c>
+      <c r="E47" t="s">
+        <v>825</v>
+      </c>
+      <c r="F47" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47" t="s">
+        <v>741</v>
+      </c>
+      <c r="I47" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>826</v>
+      </c>
+      <c r="D48" t="s">
+        <v>243</v>
+      </c>
+      <c r="E48" t="s">
+        <v>827</v>
+      </c>
+      <c r="F48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H48" t="s">
+        <v>741</v>
+      </c>
+      <c r="I48" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>828</v>
+      </c>
+      <c r="D49" t="s">
+        <v>243</v>
+      </c>
+      <c r="E49" t="s">
+        <v>829</v>
+      </c>
+      <c r="F49" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" t="s">
+        <v>741</v>
+      </c>
+      <c r="I49" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0B4E37-E48F-4CBE-B111-F24E7BD77522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01075433-743F-4100-A635-2F7732C3B6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5194,7 +5194,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE47005-90C5-46FF-AE6E-BECFAB6521D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05638AA7-D538-48AF-89B5-BD5E2FBC2085}">
   <dimension ref="B3:I49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6405,7 +6405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1D028D5-41AD-4C92-A7FC-A5B3AE889C18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B261BF51-EE46-41F8-ABA2-DC7697971729}">
   <dimension ref="B3:I49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01075433-743F-4100-A635-2F7732C3B6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CF296F-7499-452B-9E26-1C90B7FC7DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3069" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3053" uniqueCount="916">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -2364,12 +2364,6 @@
     <t>grid node -- way/164764363-275 (Adelaide, 276 km)</t>
   </si>
   <si>
-    <t>e_Dubbo_AUS</t>
-  </si>
-  <si>
-    <t>grid node -- way/169406848-330 (Central Coast, 226 km)</t>
-  </si>
-  <si>
     <t>e_GinGin_AUS</t>
   </si>
   <si>
@@ -2632,12 +2626,6 @@
   </si>
   <si>
     <t>heat at grid node -- way/164764363-275 (Adelaide, 276 km)</t>
-  </si>
-  <si>
-    <t>h_Dubbo_AUS</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/169406848-330 (Central Coast, 226 km)</t>
   </si>
   <si>
     <t>h_GinGin_AUS</t>
@@ -5194,8 +5182,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05638AA7-D538-48AF-89B5-BD5E2FBC2085}">
-  <dimension ref="B3:I49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26066F4E-0C29-4CE7-A24E-4DD8E94D40FC}">
+  <dimension ref="B3:I48"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -5234,13 +5222,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -5260,13 +5248,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -5286,13 +5274,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -5312,13 +5300,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -5338,13 +5326,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -5364,13 +5352,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -5390,13 +5378,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -5416,13 +5404,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -5442,13 +5430,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -5468,13 +5456,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -5494,13 +5482,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -5520,13 +5508,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -5546,13 +5534,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -5572,13 +5560,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -5598,13 +5586,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -5624,13 +5612,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -5650,13 +5638,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -5676,13 +5664,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -5702,13 +5690,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -5728,13 +5716,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -5754,13 +5742,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -5780,13 +5768,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -5806,13 +5794,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -5832,13 +5820,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -5858,13 +5846,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -5884,13 +5872,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -5910,13 +5898,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -5936,13 +5924,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -5962,13 +5950,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -5988,13 +5976,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -6014,13 +6002,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -6040,13 +6028,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -6066,13 +6054,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -6092,13 +6080,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -6118,13 +6106,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -6144,13 +6132,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -6170,13 +6158,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -6196,13 +6184,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -6222,13 +6210,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -6248,13 +6236,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -6274,13 +6262,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -6300,13 +6288,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -6326,13 +6314,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -6352,13 +6340,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -6370,32 +6358,6 @@
         <v>741</v>
       </c>
       <c r="I48" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="B49" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" t="s">
-        <v>918</v>
-      </c>
-      <c r="D49" t="s">
-        <v>243</v>
-      </c>
-      <c r="E49" t="s">
-        <v>919</v>
-      </c>
-      <c r="F49" t="s">
-        <v>233</v>
-      </c>
-      <c r="G49" t="s">
-        <v>232</v>
-      </c>
-      <c r="H49" t="s">
-        <v>741</v>
-      </c>
-      <c r="I49" t="s">
         <v>247</v>
       </c>
     </row>
@@ -6405,8 +6367,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B261BF51-EE46-41F8-ABA2-DC7697971729}">
-  <dimension ref="B3:I49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D98E544-EDB6-4550-9EF1-104C78550F67}">
+  <dimension ref="B3:I48"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -7581,32 +7543,6 @@
         <v>741</v>
       </c>
       <c r="I48" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="B49" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" t="s">
-        <v>828</v>
-      </c>
-      <c r="D49" t="s">
-        <v>243</v>
-      </c>
-      <c r="E49" t="s">
-        <v>829</v>
-      </c>
-      <c r="F49" t="s">
-        <v>25</v>
-      </c>
-      <c r="G49" t="s">
-        <v>35</v>
-      </c>
-      <c r="H49" t="s">
-        <v>741</v>
-      </c>
-      <c r="I49" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CF296F-7499-452B-9E26-1C90B7FC7DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3804345B-90DD-408E-BB6F-BDBF8847AF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5182,7 +5182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26066F4E-0C29-4CE7-A24E-4DD8E94D40FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3998B4FE-6E2E-432C-95B0-AA7D39A5FA5B}">
   <dimension ref="B3:I48"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6367,7 +6367,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D98E544-EDB6-4550-9EF1-104C78550F67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22F21533-1789-43EC-8A5F-8E8ED4514843}">
   <dimension ref="B3:I48"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3804345B-90DD-408E-BB6F-BDBF8847AF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BFD411-DA70-47DA-81CD-F538E71F6BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5182,7 +5182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3998B4FE-6E2E-432C-95B0-AA7D39A5FA5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C6AF67C-0001-4573-9BA1-3A5A67363CF2}">
   <dimension ref="B3:I48"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6367,7 +6367,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22F21533-1789-43EC-8A5F-8E8ED4514843}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA2C52E-3D7D-48A5-BCB7-B268545773DB}">
   <dimension ref="B3:I48"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BFD411-DA70-47DA-81CD-F538E71F6BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC5B050-DB9F-4AC8-B5EA-4AC0F459AEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3053" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3085" uniqueCount="924">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -780,7 +780,7 @@
     <t>elc_spv_AUS_001</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 1)</t>
+    <t>solar electricity near Sydney (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -789,43 +789,43 @@
     <t>elc_spv_AUS_002</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 2)</t>
+    <t>solar electricity near Bendigo (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_AUS_003</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 3)</t>
+    <t>solar electricity near Bunbury (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_AUS_004</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 4)</t>
+    <t>solar electricity near Launceston (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_AUS_005</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 5)</t>
+    <t>solar electricity near Ballarat (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_AUS_006</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 6)</t>
+    <t>solar electricity near Rockhampton (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_AUS_007</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 7)</t>
+    <t>solar electricity near Mackay (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_AUS_008</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 8)</t>
+    <t>solar electricity near Central Coast (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_AUS_009</t>
@@ -849,241 +849,241 @@
     <t>elc_spv_AUS_012</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 12)</t>
+    <t>solar electricity near Mackay (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_AUS_013</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 13)</t>
+    <t>solar electricity near Central Coast (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_AUS_014</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 14)</t>
+    <t>solar electricity near Canberra (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_AUS_015</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 15)</t>
+    <t>solar electricity near Bendigo (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_AUS_016</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 16)</t>
+    <t>solar electricity near Bendigo (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_AUS_017</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 17)</t>
+    <t>solar electricity near Toowoomba (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_AUS_018</t>
   </si>
   <si>
-    <t>solar electricity near Cairns (cluster 18)</t>
+    <t>solar electricity near Rockhampton (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_AUS_019</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 19)</t>
+    <t>solar electricity near Bundaberg (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_AUS_020</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 20)</t>
+    <t>solar electricity near Townsville (cluster 20)</t>
   </si>
   <si>
     <t>elc_spv_AUS_021</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 21)</t>
+    <t>solar electricity near Townsville (cluster 21)</t>
   </si>
   <si>
     <t>elc_spv_AUS_022</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 22)</t>
+    <t>solar electricity near Townsville (cluster 22)</t>
   </si>
   <si>
     <t>elc_spv_AUS_023</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 23)</t>
+    <t>solar electricity near Canberra (cluster 23)</t>
   </si>
   <si>
     <t>elc_spv_AUS_024</t>
   </si>
   <si>
-    <t>solar electricity near Cairns (cluster 24)</t>
+    <t>solar electricity near Adelaide (cluster 24)</t>
   </si>
   <si>
     <t>elc_spv_AUS_025</t>
   </si>
   <si>
-    <t>solar electricity near Cairns (cluster 25)</t>
+    <t>solar electricity near Brisbane (cluster 25)</t>
   </si>
   <si>
     <t>elc_spv_AUS_026</t>
   </si>
   <si>
-    <t>solar electricity near Cairns (cluster 26)</t>
+    <t>solar electricity near Toowoomba (cluster 26)</t>
   </si>
   <si>
     <t>elc_spv_AUS_027</t>
   </si>
   <si>
-    <t>solar electricity near Townsville (cluster 27)</t>
+    <t>solar electricity near Launceston (cluster 27)</t>
   </si>
   <si>
     <t>elc_spv_AUS_028</t>
   </si>
   <si>
-    <t>solar electricity near Townsville (cluster 28)</t>
+    <t>solar electricity near Canberra (cluster 28)</t>
   </si>
   <si>
     <t>elc_spv_AUS_029</t>
   </si>
   <si>
-    <t>solar electricity near Townsville (cluster 29)</t>
+    <t>solar electricity near Adelaide (cluster 29)</t>
   </si>
   <si>
     <t>elc_spv_AUS_030</t>
   </si>
   <si>
-    <t>solar electricity near Townsville (cluster 30)</t>
+    <t>solar electricity near Adelaide (cluster 30)</t>
   </si>
   <si>
     <t>elc_spv_AUS_031</t>
   </si>
   <si>
-    <t>solar electricity near Cairns (cluster 31)</t>
+    <t>solar electricity near Adelaide (cluster 31)</t>
   </si>
   <si>
     <t>elc_spv_AUS_032</t>
   </si>
   <si>
-    <t>solar electricity near Townsville (cluster 32)</t>
+    <t>solar electricity near Adelaide (cluster 32)</t>
   </si>
   <si>
     <t>elc_spv_AUS_033</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 33)</t>
+    <t>solar electricity near Adelaide (cluster 33)</t>
   </si>
   <si>
     <t>elc_spv_AUS_034</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 34)</t>
+    <t>solar electricity near Adelaide (cluster 34)</t>
   </si>
   <si>
     <t>elc_spv_AUS_035</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 35)</t>
+    <t>solar electricity near Adelaide (cluster 35)</t>
   </si>
   <si>
     <t>elc_spv_AUS_036</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 36)</t>
+    <t>solar electricity near Adelaide (cluster 36)</t>
   </si>
   <si>
     <t>elc_spv_AUS_037</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 37)</t>
+    <t>solar electricity near Adelaide (cluster 37)</t>
   </si>
   <si>
     <t>elc_spv_AUS_038</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 38)</t>
+    <t>solar electricity near Adelaide (cluster 38)</t>
   </si>
   <si>
     <t>elc_spv_AUS_039</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 39)</t>
+    <t>solar electricity near Townsville (cluster 39)</t>
   </si>
   <si>
     <t>elc_spv_AUS_040</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 40)</t>
+    <t>solar electricity near Adelaide (cluster 40)</t>
   </si>
   <si>
     <t>elc_spv_AUS_041</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 41)</t>
+    <t>solar electricity near Townsville (cluster 41)</t>
   </si>
   <si>
     <t>elc_spv_AUS_042</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 42)</t>
+    <t>solar electricity near Darwin (cluster 42)</t>
   </si>
   <si>
     <t>elc_spv_AUS_043</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 43)</t>
+    <t>solar electricity near Darwin (cluster 43)</t>
   </si>
   <si>
     <t>elc_spv_AUS_044</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 44)</t>
+    <t>solar electricity near Darwin (cluster 44)</t>
   </si>
   <si>
     <t>elc_spv_AUS_045</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 45)</t>
+    <t>solar electricity near Townsville (cluster 45)</t>
   </si>
   <si>
     <t>elc_spv_AUS_046</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 46)</t>
+    <t>solar electricity near Cairns (cluster 46)</t>
   </si>
   <si>
     <t>elc_spv_AUS_047</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 47)</t>
+    <t>solar electricity near Darwin (cluster 47)</t>
   </si>
   <si>
     <t>elc_spv_AUS_048</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 48)</t>
+    <t>solar electricity near Townsville (cluster 48)</t>
   </si>
   <si>
     <t>elc_spv_AUS_049</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 49)</t>
+    <t>solar electricity near Darwin (cluster 49)</t>
   </si>
   <si>
     <t>elc_spv_AUS_050</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 50)</t>
+    <t>solar electricity near Cairns (cluster 50)</t>
   </si>
   <si>
     <t>elc_spv_AUS_051</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 51)</t>
+    <t>solar electricity near Canberra (cluster 51)</t>
   </si>
   <si>
     <t>elc_spv_AUS_052</t>
@@ -1095,37 +1095,37 @@
     <t>elc_spv_AUS_053</t>
   </si>
   <si>
-    <t>solar electricity near Canberra (cluster 53)</t>
+    <t>solar electricity near Cranbourne (cluster 53)</t>
   </si>
   <si>
     <t>elc_spv_AUS_054</t>
   </si>
   <si>
-    <t>solar electricity near Canberra (cluster 54)</t>
+    <t>solar electricity near Ballarat (cluster 54)</t>
   </si>
   <si>
     <t>elc_spv_AUS_055</t>
   </si>
   <si>
-    <t>solar electricity near Bendigo (cluster 55)</t>
+    <t>solar electricity near Perth (cluster 55)</t>
   </si>
   <si>
     <t>elc_spv_AUS_056</t>
   </si>
   <si>
-    <t>solar electricity near Canberra (cluster 56)</t>
+    <t>solar electricity near Perth (cluster 56)</t>
   </si>
   <si>
     <t>elc_spv_AUS_057</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 57)</t>
+    <t>solar electricity near Perth (cluster 57)</t>
   </si>
   <si>
     <t>elc_spv_AUS_058</t>
   </si>
   <si>
-    <t>solar electricity near Bendigo (cluster 58)</t>
+    <t>solar electricity near Bundaberg (cluster 58)</t>
   </si>
   <si>
     <t>elc_spv_AUS_059</t>
@@ -1137,55 +1137,55 @@
     <t>elc_spv_AUS_060</t>
   </si>
   <si>
-    <t>solar electricity near Cranbourne (cluster 60)</t>
+    <t>solar electricity near Toowoomba (cluster 60)</t>
   </si>
   <si>
     <t>elc_spv_AUS_061</t>
   </si>
   <si>
-    <t>solar electricity near Cranbourne (cluster 61)</t>
+    <t>solar electricity near Toowoomba (cluster 61)</t>
   </si>
   <si>
     <t>elc_spv_AUS_062</t>
   </si>
   <si>
-    <t>solar electricity near Ballarat (cluster 62)</t>
+    <t>solar electricity near Perth (cluster 62)</t>
   </si>
   <si>
     <t>elc_spv_AUS_063</t>
   </si>
   <si>
-    <t>solar electricity near Geelong (cluster 63)</t>
+    <t>solar electricity near Perth (cluster 63)</t>
   </si>
   <si>
     <t>elc_spv_AUS_064</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 64)</t>
+    <t>solar electricity near Darwin (cluster 64)</t>
   </si>
   <si>
     <t>elc_spv_AUS_065</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 65)</t>
+    <t>solar electricity near Darwin (cluster 65)</t>
   </si>
   <si>
     <t>elc_spv_AUS_066</t>
   </si>
   <si>
-    <t>solar electricity near Launceston (cluster 66)</t>
+    <t>solar electricity near Darwin (cluster 66)</t>
   </si>
   <si>
     <t>elc_spv_AUS_067</t>
   </si>
   <si>
-    <t>solar electricity near Launceston (cluster 67)</t>
+    <t>solar electricity near Perth (cluster 67)</t>
   </si>
   <si>
     <t>elc_spv_AUS_068</t>
   </si>
   <si>
-    <t>solar electricity near Hobart (cluster 68)</t>
+    <t>solar electricity near Perth (cluster 68)</t>
   </si>
   <si>
     <t>elc_spv_AUS_069</t>
@@ -1203,13 +1203,13 @@
     <t>elc_spv_AUS_071</t>
   </si>
   <si>
-    <t>solar electricity near Bunbury (cluster 71)</t>
+    <t>solar electricity near Perth (cluster 71)</t>
   </si>
   <si>
     <t>elc_spv_AUS_072</t>
   </si>
   <si>
-    <t>solar electricity near Bunbury (cluster 72)</t>
+    <t>solar electricity near Perth (cluster 72)</t>
   </si>
   <si>
     <t>elc_spv_AUS_073</t>
@@ -1221,271 +1221,271 @@
     <t>elc_spv_AUS_074</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 74)</t>
+    <t>solar electricity near Canberra (cluster 74)</t>
   </si>
   <si>
     <t>elc_spv_AUS_075</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 75)</t>
+    <t>solar electricity near Adelaide (cluster 75)</t>
   </si>
   <si>
     <t>elc_spv_AUS_076</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 76)</t>
+    <t>solar electricity near Adelaide (cluster 76)</t>
   </si>
   <si>
     <t>elc_spv_AUS_077</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 77)</t>
+    <t>solar electricity near Rockhampton (cluster 77)</t>
   </si>
   <si>
     <t>elc_spv_AUS_078</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 78)</t>
+    <t>solar electricity near Canberra (cluster 78)</t>
   </si>
   <si>
     <t>elc_spv_AUS_079</t>
   </si>
   <si>
-    <t>solar electricity near Bundaberg (cluster 79)</t>
+    <t>solar electricity near Adelaide (cluster 79)</t>
   </si>
   <si>
     <t>elc_spv_AUS_080</t>
   </si>
   <si>
-    <t>solar electricity near Mackay (cluster 80)</t>
+    <t>solar electricity near Perth (cluster 80)</t>
   </si>
   <si>
     <t>elc_spv_AUS_081</t>
   </si>
   <si>
-    <t>solar electricity near Mackay (cluster 81)</t>
+    <t>solar electricity near Newcastle (cluster 81)</t>
   </si>
   <si>
     <t>elc_spv_AUS_082</t>
   </si>
   <si>
-    <t>solar electricity near Ipswich (cluster 82)</t>
+    <t>solar electricity near Perth (cluster 82)</t>
   </si>
   <si>
     <t>elc_spv_AUS_083</t>
   </si>
   <si>
-    <t>solar electricity near Toowoomba (cluster 83)</t>
+    <t>solar electricity near Ballarat (cluster 83)</t>
   </si>
   <si>
     <t>elc_spv_AUS_084</t>
   </si>
   <si>
-    <t>solar electricity near Toowoomba (cluster 84)</t>
+    <t>solar electricity near Darwin (cluster 84)</t>
   </si>
   <si>
     <t>elc_spv_AUS_085</t>
   </si>
   <si>
-    <t>solar electricity near Rockhampton (cluster 85)</t>
+    <t>solar electricity near Darwin (cluster 85)</t>
   </si>
   <si>
     <t>elc_spv_AUS_086</t>
   </si>
   <si>
-    <t>solar electricity near Mackay (cluster 86)</t>
+    <t>solar electricity near Perth (cluster 86)</t>
   </si>
   <si>
     <t>elc_spv_AUS_087</t>
   </si>
   <si>
-    <t>solar electricity near Rockhampton (cluster 87)</t>
+    <t>solar electricity near Darwin (cluster 87)</t>
   </si>
   <si>
     <t>elc_spv_AUS_088</t>
   </si>
   <si>
-    <t>solar electricity near Sydney (cluster 88)</t>
+    <t>solar electricity near Darwin (cluster 88)</t>
   </si>
   <si>
     <t>elc_spv_AUS_089</t>
   </si>
   <si>
-    <t>solar electricity near Canberra (cluster 89)</t>
+    <t>solar electricity near Darwin (cluster 89)</t>
   </si>
   <si>
     <t>elc_spv_AUS_090</t>
   </si>
   <si>
-    <t>solar electricity near Newcastle (cluster 90)</t>
+    <t>solar electricity near Hobart (cluster 90)</t>
   </si>
   <si>
     <t>elc_spv_AUS_091</t>
   </si>
   <si>
-    <t>solar electricity near Central Coast (cluster 91)</t>
+    <t>solar electricity near Perth (cluster 91)</t>
   </si>
   <si>
     <t>elc_spv_AUS_092</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 92)</t>
+    <t>solar electricity near Perth (cluster 92)</t>
   </si>
   <si>
     <t>elc_spv_AUS_093</t>
   </si>
   <si>
-    <t>solar electricity near Toowoomba (cluster 93)</t>
+    <t>solar electricity near Perth (cluster 93)</t>
   </si>
   <si>
     <t>elc_spv_AUS_094</t>
   </si>
   <si>
-    <t>solar electricity near Mackay (cluster 94)</t>
+    <t>solar electricity near Perth (cluster 94)</t>
   </si>
   <si>
     <t>elc_spv_AUS_095</t>
   </si>
   <si>
-    <t>solar electricity near Central Coast (cluster 95)</t>
+    <t>solar electricity near Perth (cluster 95)</t>
   </si>
   <si>
     <t>elc_spv_AUS_096</t>
   </si>
   <si>
-    <t>solar electricity near Bendigo (cluster 96)</t>
+    <t>solar electricity near Perth (cluster 96)</t>
   </si>
   <si>
     <t>elc_spv_AUS_097</t>
   </si>
   <si>
-    <t>solar electricity near Canberra (cluster 97)</t>
+    <t>solar electricity near Perth (cluster 97)</t>
   </si>
   <si>
     <t>elc_wof_AUS_001</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 1)</t>
+    <t>wind offshore electricity near Wollongong (cluster 1)</t>
   </si>
   <si>
     <t>elc_wof_AUS_002</t>
   </si>
   <si>
-    <t>wind offshore electricity near Perth (cluster 2)</t>
+    <t>wind offshore electricity near Bunbury (cluster 2)</t>
   </si>
   <si>
     <t>elc_wof_AUS_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 3)</t>
+    <t>wind offshore electricity near Launceston (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_AUS_004</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 4)</t>
+    <t>wind offshore electricity near Launceston (cluster 4)</t>
   </si>
   <si>
     <t>elc_wof_AUS_005</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 5)</t>
+    <t>wind offshore electricity near Geelong (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_AUS_006</t>
   </si>
   <si>
-    <t>wind offshore electricity near Cranbourne (cluster 6)</t>
+    <t>wind offshore electricity near Mackay (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_AUS_007</t>
   </si>
   <si>
-    <t>wind offshore electricity near Canberra (cluster 7)</t>
+    <t>wind offshore electricity near Newcastle (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_AUS_008</t>
   </si>
   <si>
-    <t>wind offshore electricity near Hobart (cluster 8)</t>
+    <t>wind offshore electricity near Adelaide (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_AUS_009</t>
   </si>
   <si>
-    <t>wind offshore electricity near Hobart (cluster 9)</t>
+    <t>wind offshore electricity near Adelaide (cluster 9)</t>
   </si>
   <si>
     <t>elc_wof_AUS_010</t>
   </si>
   <si>
-    <t>wind offshore electricity near Geelong (cluster 10)</t>
+    <t>wind offshore electricity near Mackay (cluster 10)</t>
   </si>
   <si>
     <t>elc_wof_AUS_011</t>
   </si>
   <si>
-    <t>wind offshore electricity near Geelong (cluster 11)</t>
+    <t>wind offshore electricity near Mackay (cluster 11)</t>
   </si>
   <si>
     <t>elc_wof_AUS_012</t>
   </si>
   <si>
-    <t>wind offshore electricity near Cranbourne (cluster 12)</t>
+    <t>wind offshore electricity near Maroochydore (cluster 12)</t>
   </si>
   <si>
     <t>elc_wof_AUS_013</t>
   </si>
   <si>
-    <t>wind offshore electricity near Launceston (cluster 13)</t>
+    <t>wind offshore electricity near Mackay (cluster 13)</t>
   </si>
   <si>
     <t>elc_wof_AUS_014</t>
   </si>
   <si>
-    <t>wind offshore electricity near Perth (cluster 14)</t>
+    <t>wind offshore electricity near Bundaberg (cluster 14)</t>
   </si>
   <si>
     <t>elc_wof_AUS_015</t>
   </si>
   <si>
-    <t>wind offshore electricity near Perth (cluster 15)</t>
+    <t>wind offshore electricity near Townsville (cluster 15)</t>
   </si>
   <si>
     <t>elc_wof_AUS_016</t>
   </si>
   <si>
-    <t>wind offshore electricity near Mandurah (cluster 16)</t>
+    <t>wind offshore electricity near Townsville (cluster 16)</t>
   </si>
   <si>
     <t>elc_wof_AUS_017</t>
   </si>
   <si>
-    <t>wind offshore electricity near Bunbury (cluster 17)</t>
+    <t>wind offshore electricity near Adelaide (cluster 17)</t>
   </si>
   <si>
     <t>elc_wof_AUS_018</t>
   </si>
   <si>
-    <t>wind offshore electricity near Bunbury (cluster 18)</t>
+    <t>wind offshore electricity near Adelaide (cluster 18)</t>
   </si>
   <si>
     <t>elc_wof_AUS_019</t>
   </si>
   <si>
-    <t>wind offshore electricity near Adelaide (cluster 19)</t>
+    <t>wind offshore electricity near Gold Coast (cluster 19)</t>
   </si>
   <si>
     <t>elc_wof_AUS_020</t>
   </si>
   <si>
-    <t>wind offshore electricity near Adelaide (cluster 20)</t>
+    <t>wind offshore electricity near Launceston (cluster 20)</t>
   </si>
   <si>
     <t>elc_wof_AUS_021</t>
   </si>
   <si>
-    <t>wind offshore electricity near Adelaide (cluster 21)</t>
+    <t>wind offshore electricity near Canberra (cluster 21)</t>
   </si>
   <si>
     <t>elc_wof_AUS_022</t>
@@ -1503,403 +1503,403 @@
     <t>elc_wof_AUS_024</t>
   </si>
   <si>
-    <t>wind offshore electricity near Adelaide (cluster 24)</t>
+    <t>wind offshore electricity near Cairns (cluster 24)</t>
   </si>
   <si>
     <t>elc_wof_AUS_025</t>
   </si>
   <si>
-    <t>wind offshore electricity near Perth (cluster 25)</t>
+    <t>wind offshore electricity near Cairns (cluster 25)</t>
   </si>
   <si>
     <t>elc_wof_AUS_026</t>
   </si>
   <si>
-    <t>wind offshore electricity near Perth (cluster 26)</t>
+    <t>wind offshore electricity near Cairns (cluster 26)</t>
   </si>
   <si>
     <t>elc_wof_AUS_027</t>
   </si>
   <si>
-    <t>wind offshore electricity near Perth (cluster 27)</t>
+    <t>wind offshore electricity near Darwin (cluster 27)</t>
   </si>
   <si>
     <t>elc_wof_AUS_028</t>
   </si>
   <si>
-    <t>wind offshore electricity near Perth (cluster 28)</t>
+    <t>wind offshore electricity near Cairns (cluster 28)</t>
   </si>
   <si>
     <t>elc_wof_AUS_029</t>
   </si>
   <si>
-    <t>wind offshore electricity near Perth (cluster 29)</t>
+    <t>wind offshore electricity near Canberra (cluster 29)</t>
   </si>
   <si>
     <t>elc_wof_AUS_030</t>
   </si>
   <si>
-    <t>wind offshore electricity near Perth (cluster 30)</t>
+    <t>wind offshore electricity near Mandurah (cluster 30)</t>
   </si>
   <si>
     <t>elc_wof_AUS_031</t>
   </si>
   <si>
-    <t>wind offshore electricity near Hervey Bay (cluster 31)</t>
+    <t>wind offshore electricity near Melbourne (cluster 31)</t>
   </si>
   <si>
     <t>elc_wof_AUS_032</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gold Coast (cluster 32)</t>
+    <t>wind offshore electricity near Geelong (cluster 32)</t>
   </si>
   <si>
     <t>elc_wof_AUS_033</t>
   </si>
   <si>
-    <t>wind offshore electricity near Brisbane (cluster 33)</t>
+    <t>wind offshore electricity near Perth (cluster 33)</t>
   </si>
   <si>
     <t>elc_wof_AUS_034</t>
   </si>
   <si>
-    <t>wind offshore electricity near Sydney (cluster 34)</t>
+    <t>wind offshore electricity near Bundaberg (cluster 34)</t>
   </si>
   <si>
     <t>elc_wof_AUS_035</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gold Coast (cluster 35)</t>
+    <t>wind offshore electricity near Mackay (cluster 35)</t>
   </si>
   <si>
     <t>elc_wof_AUS_036</t>
   </si>
   <si>
-    <t>wind offshore electricity near Newcastle (cluster 36)</t>
+    <t>wind offshore electricity near Cranbourne (cluster 36)</t>
   </si>
   <si>
     <t>elc_wof_AUS_037</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 37)</t>
+    <t>wind offshore electricity near Cranbourne (cluster 37)</t>
   </si>
   <si>
     <t>elc_wof_AUS_038</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 38)</t>
+    <t>wind offshore electricity near Perth (cluster 38)</t>
   </si>
   <si>
     <t>elc_wof_AUS_039</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 39)</t>
+    <t>wind offshore electricity near Perth (cluster 39)</t>
   </si>
   <si>
     <t>elc_wof_AUS_040</t>
   </si>
   <si>
-    <t>wind offshore electricity near Cairns (cluster 40)</t>
+    <t>wind offshore electricity near Perth (cluster 40)</t>
   </si>
   <si>
     <t>elc_wof_AUS_041</t>
   </si>
   <si>
-    <t>wind offshore electricity near Cairns (cluster 41)</t>
+    <t>wind offshore electricity near Perth (cluster 41)</t>
   </si>
   <si>
     <t>elc_wof_AUS_042</t>
   </si>
   <si>
-    <t>wind offshore electricity near Cairns (cluster 42)</t>
+    <t>wind offshore electricity near Canberra (cluster 42)</t>
   </si>
   <si>
     <t>elc_wof_AUS_043</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 43)</t>
+    <t>wind offshore electricity near Perth (cluster 43)</t>
   </si>
   <si>
     <t>elc_wof_AUS_044</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 44)</t>
+    <t>wind offshore electricity near Newcastle (cluster 44)</t>
   </si>
   <si>
     <t>elc_wof_AUS_045</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 45)</t>
+    <t>wind offshore electricity near Mandurah (cluster 45)</t>
   </si>
   <si>
     <t>elc_wof_AUS_046</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 46)</t>
+    <t>wind offshore electricity near Adelaide (cluster 46)</t>
   </si>
   <si>
     <t>elc_wof_AUS_047</t>
   </si>
   <si>
-    <t>wind offshore electricity near Bundaberg (cluster 47)</t>
+    <t>wind offshore electricity near Darwin (cluster 47)</t>
   </si>
   <si>
     <t>elc_wof_AUS_048</t>
   </si>
   <si>
-    <t>wind offshore electricity near Mackay (cluster 48)</t>
+    <t>wind offshore electricity near Darwin (cluster 48)</t>
   </si>
   <si>
     <t>elc_wof_AUS_049</t>
   </si>
   <si>
-    <t>wind offshore electricity near Cairns (cluster 49)</t>
+    <t>wind offshore electricity near Darwin (cluster 49)</t>
   </si>
   <si>
     <t>elc_wof_AUS_050</t>
   </si>
   <si>
-    <t>wind offshore electricity near Cairns (cluster 50)</t>
+    <t>wind offshore electricity near Hobart (cluster 50)</t>
   </si>
   <si>
     <t>elc_wof_AUS_051</t>
   </si>
   <si>
-    <t>wind offshore electricity near Townsville (cluster 51)</t>
+    <t>wind offshore electricity near Perth (cluster 51)</t>
   </si>
   <si>
     <t>elc_wof_AUS_052</t>
   </si>
   <si>
-    <t>wind offshore electricity near Townsville (cluster 52)</t>
+    <t>wind offshore electricity near Perth (cluster 52)</t>
   </si>
   <si>
     <t>elc_won_AUS_001</t>
   </si>
   <si>
-    <t>wind onshore electricity near Cairns (cluster 1)</t>
+    <t>wind onshore electricity near Wollongong (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_AUS_002</t>
   </si>
   <si>
-    <t>wind onshore electricity near Cairns (cluster 2)</t>
+    <t>wind onshore electricity near Bendigo (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_AUS_003</t>
   </si>
   <si>
-    <t>wind onshore electricity near Cairns (cluster 3)</t>
+    <t>wind onshore electricity near Bunbury (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_AUS_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Cairns (cluster 4)</t>
+    <t>wind onshore electricity near Launceston (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_AUS_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Townsville (cluster 5)</t>
+    <t>wind onshore electricity near Ballarat (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_AUS_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Townsville (cluster 6)</t>
+    <t>wind onshore electricity near Rockhampton (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_AUS_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Townsville (cluster 7)</t>
+    <t>wind onshore electricity near Mackay (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_AUS_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mackay (cluster 8)</t>
+    <t>wind onshore electricity near Newcastle (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_AUS_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Townsville (cluster 9)</t>
+    <t>wind onshore electricity near Adelaide (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_AUS_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Cairns (cluster 10)</t>
+    <t>wind onshore electricity near Adelaide (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_AUS_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Cairns (cluster 11)</t>
+    <t>wind onshore electricity near Adelaide (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_AUS_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 12)</t>
+    <t>wind onshore electricity near Mackay (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_AUS_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Cairns (cluster 13)</t>
+    <t>wind onshore electricity near Central Coast (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_AUS_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 14)</t>
+    <t>wind onshore electricity near Bendigo (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_AUS_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 15)</t>
+    <t>wind onshore electricity near Canberra (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_AUS_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Townsville (cluster 16)</t>
+    <t>wind onshore electricity near Bendigo (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_AUS_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 17)</t>
+    <t>wind onshore electricity near Toowoomba (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_AUS_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 18)</t>
+    <t>wind onshore electricity near Rockhampton (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_AUS_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 19)</t>
+    <t>wind onshore electricity near Bundaberg (cluster 19)</t>
   </si>
   <si>
     <t>elc_won_AUS_020</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 20)</t>
+    <t>wind onshore electricity near Townsville (cluster 20)</t>
   </si>
   <si>
     <t>elc_won_AUS_021</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 21)</t>
+    <t>wind onshore electricity near Townsville (cluster 21)</t>
   </si>
   <si>
     <t>elc_won_AUS_022</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 22)</t>
+    <t>wind onshore electricity near Canberra (cluster 22)</t>
   </si>
   <si>
     <t>elc_won_AUS_023</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 23)</t>
+    <t>wind onshore electricity near Adelaide (cluster 23)</t>
   </si>
   <si>
     <t>elc_won_AUS_024</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 24)</t>
+    <t>wind onshore electricity near Brisbane (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_AUS_025</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 25)</t>
+    <t>wind onshore electricity near Toowoomba (cluster 25)</t>
   </si>
   <si>
     <t>elc_won_AUS_026</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 26)</t>
+    <t>wind onshore electricity near Hobart (cluster 26)</t>
   </si>
   <si>
     <t>elc_won_AUS_027</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 27)</t>
+    <t>wind onshore electricity near Canberra (cluster 27)</t>
   </si>
   <si>
     <t>elc_won_AUS_028</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 28)</t>
+    <t>wind onshore electricity near Adelaide (cluster 28)</t>
   </si>
   <si>
     <t>elc_won_AUS_029</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 29)</t>
+    <t>wind onshore electricity near Adelaide (cluster 29)</t>
   </si>
   <si>
     <t>elc_won_AUS_030</t>
   </si>
   <si>
-    <t>wind onshore electricity near Melbourne (cluster 30)</t>
+    <t>wind onshore electricity near Adelaide (cluster 30)</t>
   </si>
   <si>
     <t>elc_won_AUS_031</t>
   </si>
   <si>
-    <t>wind onshore electricity near Canberra (cluster 31)</t>
+    <t>wind onshore electricity near Adelaide (cluster 31)</t>
   </si>
   <si>
     <t>elc_won_AUS_032</t>
   </si>
   <si>
-    <t>wind onshore electricity near Hobart (cluster 32)</t>
+    <t>wind onshore electricity near Adelaide (cluster 32)</t>
   </si>
   <si>
     <t>elc_won_AUS_033</t>
   </si>
   <si>
-    <t>wind onshore electricity near Cranbourne (cluster 33)</t>
+    <t>wind onshore electricity near Adelaide (cluster 33)</t>
   </si>
   <si>
     <t>elc_won_AUS_034</t>
   </si>
   <si>
-    <t>wind onshore electricity near Ballarat (cluster 34)</t>
+    <t>wind onshore electricity near Darwin (cluster 34)</t>
   </si>
   <si>
     <t>elc_won_AUS_035</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 35)</t>
+    <t>wind onshore electricity near Darwin (cluster 35)</t>
   </si>
   <si>
     <t>elc_won_AUS_036</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 36)</t>
+    <t>wind onshore electricity near Darwin (cluster 36)</t>
   </si>
   <si>
     <t>elc_won_AUS_037</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bendigo (cluster 37)</t>
+    <t>wind onshore electricity near Darwin (cluster 37)</t>
   </si>
   <si>
     <t>elc_won_AUS_038</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 38)</t>
+    <t>wind onshore electricity near Townsville (cluster 38)</t>
   </si>
   <si>
     <t>elc_won_AUS_039</t>
@@ -1911,25 +1911,25 @@
     <t>elc_won_AUS_040</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 40)</t>
+    <t>wind onshore electricity near Townsville (cluster 40)</t>
   </si>
   <si>
     <t>elc_won_AUS_041</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mackay (cluster 41)</t>
+    <t>wind onshore electricity near Darwin (cluster 41)</t>
   </si>
   <si>
     <t>elc_won_AUS_042</t>
   </si>
   <si>
-    <t>wind onshore electricity near Townsville (cluster 42)</t>
+    <t>wind onshore electricity near Adelaide (cluster 42)</t>
   </si>
   <si>
     <t>elc_won_AUS_043</t>
   </si>
   <si>
-    <t>wind onshore electricity near Townsville (cluster 43)</t>
+    <t>wind onshore electricity near Adelaide (cluster 43)</t>
   </si>
   <si>
     <t>elc_won_AUS_044</t>
@@ -1941,79 +1941,79 @@
     <t>elc_won_AUS_045</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 45)</t>
+    <t>wind onshore electricity near Townsville (cluster 45)</t>
   </si>
   <si>
     <t>elc_won_AUS_046</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mackay (cluster 46)</t>
+    <t>wind onshore electricity near Darwin (cluster 46)</t>
   </si>
   <si>
     <t>elc_won_AUS_047</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 47)</t>
+    <t>wind onshore electricity near Cairns (cluster 47)</t>
   </si>
   <si>
     <t>elc_won_AUS_048</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 48)</t>
+    <t>wind onshore electricity near Cairns (cluster 48)</t>
   </si>
   <si>
     <t>elc_won_AUS_049</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 49)</t>
+    <t>wind onshore electricity near Darwin (cluster 49)</t>
   </si>
   <si>
     <t>elc_won_AUS_050</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 50)</t>
+    <t>wind onshore electricity near Townsville (cluster 50)</t>
   </si>
   <si>
     <t>elc_won_AUS_051</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 51)</t>
+    <t>wind onshore electricity near Canberra (cluster 51)</t>
   </si>
   <si>
     <t>elc_won_AUS_052</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 52)</t>
+    <t>wind onshore electricity near Perth (cluster 52)</t>
   </si>
   <si>
     <t>elc_won_AUS_053</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 53)</t>
+    <t>wind onshore electricity near Cranbourne (cluster 53)</t>
   </si>
   <si>
     <t>elc_won_AUS_054</t>
   </si>
   <si>
-    <t>wind onshore electricity near Toowoomba (cluster 54)</t>
+    <t>wind onshore electricity near Ballarat (cluster 54)</t>
   </si>
   <si>
     <t>elc_won_AUS_055</t>
   </si>
   <si>
-    <t>wind onshore electricity near Toowoomba (cluster 55)</t>
+    <t>wind onshore electricity near Perth (cluster 55)</t>
   </si>
   <si>
     <t>elc_won_AUS_056</t>
   </si>
   <si>
-    <t>wind onshore electricity near Ipswich (cluster 56)</t>
+    <t>wind onshore electricity near Perth (cluster 56)</t>
   </si>
   <si>
     <t>elc_won_AUS_057</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gold Coast (cluster 57)</t>
+    <t>wind onshore electricity near Perth (cluster 57)</t>
   </si>
   <si>
     <t>elc_won_AUS_058</t>
@@ -2025,61 +2025,61 @@
     <t>elc_won_AUS_059</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bundaberg (cluster 59)</t>
+    <t>wind onshore electricity near Cranbourne (cluster 59)</t>
   </si>
   <si>
     <t>elc_won_AUS_060</t>
   </si>
   <si>
-    <t>wind onshore electricity near Newcastle (cluster 60)</t>
+    <t>wind onshore electricity near Toowoomba (cluster 60)</t>
   </si>
   <si>
     <t>elc_won_AUS_061</t>
   </si>
   <si>
-    <t>wind onshore electricity near Central Coast (cluster 61)</t>
+    <t>wind onshore electricity near Toowoomba (cluster 61)</t>
   </si>
   <si>
     <t>elc_won_AUS_062</t>
   </si>
   <si>
-    <t>wind onshore electricity near Canberra (cluster 62)</t>
+    <t>wind onshore electricity near Perth (cluster 62)</t>
   </si>
   <si>
     <t>elc_won_AUS_063</t>
   </si>
   <si>
-    <t>wind onshore electricity near Newcastle (cluster 63)</t>
+    <t>wind onshore electricity near Perth (cluster 63)</t>
   </si>
   <si>
     <t>elc_won_AUS_064</t>
   </si>
   <si>
-    <t>wind onshore electricity near Newcastle (cluster 64)</t>
+    <t>wind onshore electricity near Darwin (cluster 64)</t>
   </si>
   <si>
     <t>elc_won_AUS_065</t>
   </si>
   <si>
-    <t>wind onshore electricity near Canberra (cluster 65)</t>
+    <t>wind onshore electricity near Darwin (cluster 65)</t>
   </si>
   <si>
     <t>elc_won_AUS_066</t>
   </si>
   <si>
-    <t>wind onshore electricity near Toowoomba (cluster 66)</t>
+    <t>wind onshore electricity near Perth (cluster 66)</t>
   </si>
   <si>
     <t>elc_won_AUS_067</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bendigo (cluster 67)</t>
+    <t>wind onshore electricity near Perth (cluster 67)</t>
   </si>
   <si>
     <t>elc_won_AUS_068</t>
   </si>
   <si>
-    <t>wind onshore electricity near Sydney (cluster 68)</t>
+    <t>wind onshore electricity near Perth (cluster 68)</t>
   </si>
   <si>
     <t>elc_won_AUS_069</t>
@@ -2115,37 +2115,37 @@
     <t>elc_won_AUS_074</t>
   </si>
   <si>
-    <t>wind onshore electricity near Perth (cluster 74)</t>
+    <t>wind onshore electricity near Canberra (cluster 74)</t>
   </si>
   <si>
     <t>elc_won_AUS_075</t>
   </si>
   <si>
-    <t>wind onshore electricity near Perth (cluster 75)</t>
+    <t>wind onshore electricity near Adelaide (cluster 75)</t>
   </si>
   <si>
     <t>elc_won_AUS_076</t>
   </si>
   <si>
-    <t>wind onshore electricity near Perth (cluster 76)</t>
+    <t>wind onshore electricity near Adelaide (cluster 76)</t>
   </si>
   <si>
     <t>elc_won_AUS_077</t>
   </si>
   <si>
-    <t>wind onshore electricity near Perth (cluster 77)</t>
+    <t>wind onshore electricity near Rockhampton (cluster 77)</t>
   </si>
   <si>
     <t>elc_won_AUS_078</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bunbury (cluster 78)</t>
+    <t>wind onshore electricity near Adelaide (cluster 78)</t>
   </si>
   <si>
     <t>elc_won_AUS_079</t>
   </si>
   <si>
-    <t>wind onshore electricity near Perth (cluster 79)</t>
+    <t>wind onshore electricity near Adelaide (cluster 79)</t>
   </si>
   <si>
     <t>elc_won_AUS_080</t>
@@ -2157,7 +2157,7 @@
     <t>elc_won_AUS_081</t>
   </si>
   <si>
-    <t>wind onshore electricity near Perth (cluster 81)</t>
+    <t>wind onshore electricity near Newcastle (cluster 81)</t>
   </si>
   <si>
     <t>elc_won_AUS_082</t>
@@ -2169,19 +2169,19 @@
     <t>elc_won_AUS_083</t>
   </si>
   <si>
-    <t>wind onshore electricity near Perth (cluster 83)</t>
+    <t>wind onshore electricity near Ballarat (cluster 83)</t>
   </si>
   <si>
     <t>elc_won_AUS_084</t>
   </si>
   <si>
-    <t>wind onshore electricity near Perth (cluster 84)</t>
+    <t>wind onshore electricity near Darwin (cluster 84)</t>
   </si>
   <si>
     <t>elc_won_AUS_085</t>
   </si>
   <si>
-    <t>wind onshore electricity near Perth (cluster 85)</t>
+    <t>wind onshore electricity near Darwin (cluster 85)</t>
   </si>
   <si>
     <t>elc_won_AUS_086</t>
@@ -2205,7 +2205,7 @@
     <t>elc_won_AUS_089</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 89)</t>
+    <t>wind onshore electricity near Hobart (cluster 89)</t>
   </si>
   <si>
     <t>elc_won_AUS_090</t>
@@ -2217,13 +2217,13 @@
     <t>elc_won_AUS_091</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 91)</t>
+    <t>wind onshore electricity near Perth (cluster 91)</t>
   </si>
   <si>
     <t>elc_won_AUS_092</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 92)</t>
+    <t>wind onshore electricity near Perth (cluster 92)</t>
   </si>
   <si>
     <t>elc_won_AUS_093</t>
@@ -2268,6 +2268,12 @@
     <t>lo</t>
   </si>
   <si>
+    <t>e_AUS42p8S146p2E_AUS</t>
+  </si>
+  <si>
+    <t>grid node -- AU149-220 (Hobart, 94 km)</t>
+  </si>
+  <si>
     <t>e_Armidale_AUS</t>
   </si>
   <si>
@@ -2424,6 +2430,12 @@
     <t>grid node -- way/166113109-275 (Mackay, 75 km)</t>
   </si>
   <si>
+    <t>e_OlympicDamWest_AUS</t>
+  </si>
+  <si>
+    <t>grid node -- way/185835127-275 (Adelaide, 524 km)</t>
+  </si>
+  <si>
     <t>e_Palmerston_AUS</t>
   </si>
   <si>
@@ -2532,6 +2544,12 @@
     <t>heat at grid node -- way/583506664-220 (Perth, 1050 km)</t>
   </si>
   <si>
+    <t>h_AUS42p8S146p2E_AUS</t>
+  </si>
+  <si>
+    <t>heat at grid node -- AU149-220 (Hobart, 94 km)</t>
+  </si>
+  <si>
     <t>h_Armidale_AUS</t>
   </si>
   <si>
@@ -2686,6 +2704,12 @@
   </si>
   <si>
     <t>heat at grid node -- way/166113109-275 (Mackay, 75 km)</t>
+  </si>
+  <si>
+    <t>h_OlympicDamWest_AUS</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/185835127-275 (Adelaide, 524 km)</t>
   </si>
   <si>
     <t>h_Palmerston_AUS</t>
@@ -5182,8 +5206,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C6AF67C-0001-4573-9BA1-3A5A67363CF2}">
-  <dimension ref="B3:I48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E70504EF-DC36-4BC9-8E62-D5CFAD92A664}">
+  <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -5222,13 +5246,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -5248,13 +5272,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -5274,13 +5298,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -5300,13 +5324,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -5326,13 +5350,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -5352,13 +5376,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -5378,13 +5402,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -5404,13 +5428,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -5430,13 +5454,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -5456,13 +5480,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -5482,13 +5506,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -5508,13 +5532,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -5534,13 +5558,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -5560,13 +5584,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -5586,13 +5610,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -5612,13 +5636,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -5638,13 +5662,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -5664,13 +5688,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -5690,13 +5714,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -5716,13 +5740,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -5742,13 +5766,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -5768,13 +5792,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -5794,13 +5818,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -5820,13 +5844,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -5846,13 +5870,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -5872,13 +5896,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -5898,13 +5922,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -5924,13 +5948,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -5950,13 +5974,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -5976,13 +6000,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -6002,13 +6026,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -6028,13 +6052,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -6054,13 +6078,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -6080,13 +6104,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -6106,13 +6130,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -6132,13 +6156,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -6158,13 +6182,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -6184,13 +6208,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -6210,13 +6234,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -6236,13 +6260,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -6262,13 +6286,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -6288,13 +6312,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -6314,13 +6338,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -6340,13 +6364,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -6358,6 +6382,58 @@
         <v>741</v>
       </c>
       <c r="I48" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>920</v>
+      </c>
+      <c r="D49" t="s">
+        <v>243</v>
+      </c>
+      <c r="E49" t="s">
+        <v>921</v>
+      </c>
+      <c r="F49" t="s">
+        <v>233</v>
+      </c>
+      <c r="G49" t="s">
+        <v>232</v>
+      </c>
+      <c r="H49" t="s">
+        <v>741</v>
+      </c>
+      <c r="I49" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" t="s">
+        <v>922</v>
+      </c>
+      <c r="D50" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" t="s">
+        <v>923</v>
+      </c>
+      <c r="F50" t="s">
+        <v>233</v>
+      </c>
+      <c r="G50" t="s">
+        <v>232</v>
+      </c>
+      <c r="H50" t="s">
+        <v>741</v>
+      </c>
+      <c r="I50" t="s">
         <v>247</v>
       </c>
     </row>
@@ -6367,8 +6443,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA2C52E-3D7D-48A5-BCB7-B268545773DB}">
-  <dimension ref="B3:I48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18435DD2-3B91-46CF-BF31-1BC8575AA743}">
+  <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -7543,6 +7619,58 @@
         <v>741</v>
       </c>
       <c r="I48" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>828</v>
+      </c>
+      <c r="D49" t="s">
+        <v>243</v>
+      </c>
+      <c r="E49" t="s">
+        <v>829</v>
+      </c>
+      <c r="F49" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" t="s">
+        <v>741</v>
+      </c>
+      <c r="I49" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" t="s">
+        <v>830</v>
+      </c>
+      <c r="D50" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" t="s">
+        <v>831</v>
+      </c>
+      <c r="F50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" t="s">
+        <v>35</v>
+      </c>
+      <c r="H50" t="s">
+        <v>741</v>
+      </c>
+      <c r="I50" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC5B050-DB9F-4AC8-B5EA-4AC0F459AEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D39EEF-A623-4548-AB17-A89DD056C8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1827,7 +1827,7 @@
     <t>elc_won_AUS_026</t>
   </si>
   <si>
-    <t>wind onshore electricity near Hobart (cluster 26)</t>
+    <t>wind onshore electricity near Launceston (cluster 26)</t>
   </si>
   <si>
     <t>elc_won_AUS_027</t>
@@ -2268,12 +2268,6 @@
     <t>lo</t>
   </si>
   <si>
-    <t>e_AUS42p8S146p2E_AUS</t>
-  </si>
-  <si>
-    <t>grid node -- AU149-220 (Hobart, 94 km)</t>
-  </si>
-  <si>
     <t>e_Armidale_AUS</t>
   </si>
   <si>
@@ -2382,6 +2376,12 @@
     <t>grid node -- way/480009927-500 (Cranbourne, 102 km)</t>
   </si>
   <si>
+    <t>e_Hobart_AUS</t>
+  </si>
+  <si>
+    <t>grid node -- AU146-220 (Hobart, 50 km)</t>
+  </si>
+  <si>
     <t>e_Horsham_AUS</t>
   </si>
   <si>
@@ -2544,12 +2544,6 @@
     <t>heat at grid node -- way/583506664-220 (Perth, 1050 km)</t>
   </si>
   <si>
-    <t>h_AUS42p8S146p2E_AUS</t>
-  </si>
-  <si>
-    <t>heat at grid node -- AU149-220 (Hobart, 94 km)</t>
-  </si>
-  <si>
     <t>h_Armidale_AUS</t>
   </si>
   <si>
@@ -2656,6 +2650,12 @@
   </si>
   <si>
     <t>heat at grid node -- way/480009927-500 (Cranbourne, 102 km)</t>
+  </si>
+  <si>
+    <t>h_Hobart_AUS</t>
+  </si>
+  <si>
+    <t>heat at grid node -- AU146-220 (Hobart, 50 km)</t>
   </si>
   <si>
     <t>h_Horsham_AUS</t>
@@ -5206,7 +5206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E70504EF-DC36-4BC9-8E62-D5CFAD92A664}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AAF3913-2173-4E01-ACB1-9AD0E2C5F306}">
   <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6443,7 +6443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18435DD2-3B91-46CF-BF31-1BC8575AA743}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1809D02-F27F-47CE-9096-5E1B2FAA398C}">
   <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D39EEF-A623-4548-AB17-A89DD056C8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443156C0-0EAE-4EB1-8221-059840C79F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -885,19 +885,19 @@
     <t>elc_spv_AUS_018</t>
   </si>
   <si>
-    <t>solar electricity near Rockhampton (cluster 18)</t>
+    <t>solar electricity near Brisbane (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_AUS_019</t>
   </si>
   <si>
-    <t>solar electricity near Bundaberg (cluster 19)</t>
+    <t>solar electricity near Rockhampton (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_AUS_020</t>
   </si>
   <si>
-    <t>solar electricity near Townsville (cluster 20)</t>
+    <t>solar electricity near Bundaberg (cluster 20)</t>
   </si>
   <si>
     <t>elc_spv_AUS_021</t>
@@ -915,19 +915,19 @@
     <t>elc_spv_AUS_023</t>
   </si>
   <si>
-    <t>solar electricity near Canberra (cluster 23)</t>
+    <t>solar electricity near Townsville (cluster 23)</t>
   </si>
   <si>
     <t>elc_spv_AUS_024</t>
   </si>
   <si>
-    <t>solar electricity near Adelaide (cluster 24)</t>
+    <t>solar electricity near Canberra (cluster 24)</t>
   </si>
   <si>
     <t>elc_spv_AUS_025</t>
   </si>
   <si>
-    <t>solar electricity near Brisbane (cluster 25)</t>
+    <t>solar electricity near Adelaide (cluster 25)</t>
   </si>
   <si>
     <t>elc_spv_AUS_026</t>
@@ -1281,7 +1281,7 @@
     <t>elc_spv_AUS_084</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 84)</t>
+    <t>solar electricity near Hobart (cluster 84)</t>
   </si>
   <si>
     <t>elc_spv_AUS_085</t>
@@ -1293,13 +1293,13 @@
     <t>elc_spv_AUS_086</t>
   </si>
   <si>
-    <t>solar electricity near Perth (cluster 86)</t>
+    <t>solar electricity near Darwin (cluster 86)</t>
   </si>
   <si>
     <t>elc_spv_AUS_087</t>
   </si>
   <si>
-    <t>solar electricity near Darwin (cluster 87)</t>
+    <t>solar electricity near Perth (cluster 87)</t>
   </si>
   <si>
     <t>elc_spv_AUS_088</t>
@@ -1317,7 +1317,7 @@
     <t>elc_spv_AUS_090</t>
   </si>
   <si>
-    <t>solar electricity near Hobart (cluster 90)</t>
+    <t>solar electricity near Darwin (cluster 90)</t>
   </si>
   <si>
     <t>elc_spv_AUS_091</t>
@@ -1377,7 +1377,7 @@
     <t>elc_wof_AUS_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Launceston (cluster 3)</t>
+    <t>wind offshore electricity near Bunbury (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_AUS_004</t>
@@ -1389,25 +1389,25 @@
     <t>elc_wof_AUS_005</t>
   </si>
   <si>
-    <t>wind offshore electricity near Geelong (cluster 5)</t>
+    <t>wind offshore electricity near Launceston (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_AUS_006</t>
   </si>
   <si>
-    <t>wind offshore electricity near Mackay (cluster 6)</t>
+    <t>wind offshore electricity near Geelong (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_AUS_007</t>
   </si>
   <si>
-    <t>wind offshore electricity near Newcastle (cluster 7)</t>
+    <t>wind offshore electricity near Mackay (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_AUS_008</t>
   </si>
   <si>
-    <t>wind offshore electricity near Adelaide (cluster 8)</t>
+    <t>wind offshore electricity near Gold Coast (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_AUS_009</t>
@@ -1419,7 +1419,7 @@
     <t>elc_wof_AUS_010</t>
   </si>
   <si>
-    <t>wind offshore electricity near Mackay (cluster 10)</t>
+    <t>wind offshore electricity near Adelaide (cluster 10)</t>
   </si>
   <si>
     <t>elc_wof_AUS_011</t>
@@ -1431,25 +1431,25 @@
     <t>elc_wof_AUS_012</t>
   </si>
   <si>
-    <t>wind offshore electricity near Maroochydore (cluster 12)</t>
+    <t>wind offshore electricity near Mackay (cluster 12)</t>
   </si>
   <si>
     <t>elc_wof_AUS_013</t>
   </si>
   <si>
-    <t>wind offshore electricity near Mackay (cluster 13)</t>
+    <t>wind offshore electricity near Brisbane (cluster 13)</t>
   </si>
   <si>
     <t>elc_wof_AUS_014</t>
   </si>
   <si>
-    <t>wind offshore electricity near Bundaberg (cluster 14)</t>
+    <t>wind offshore electricity near Mackay (cluster 14)</t>
   </si>
   <si>
     <t>elc_wof_AUS_015</t>
   </si>
   <si>
-    <t>wind offshore electricity near Townsville (cluster 15)</t>
+    <t>wind offshore electricity near Bundaberg (cluster 15)</t>
   </si>
   <si>
     <t>elc_wof_AUS_016</t>
@@ -1461,7 +1461,7 @@
     <t>elc_wof_AUS_017</t>
   </si>
   <si>
-    <t>wind offshore electricity near Adelaide (cluster 17)</t>
+    <t>wind offshore electricity near Townsville (cluster 17)</t>
   </si>
   <si>
     <t>elc_wof_AUS_018</t>
@@ -1473,7 +1473,7 @@
     <t>elc_wof_AUS_019</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gold Coast (cluster 19)</t>
+    <t>wind offshore electricity near Adelaide (cluster 19)</t>
   </si>
   <si>
     <t>elc_wof_AUS_020</t>
@@ -1641,7 +1641,7 @@
     <t>elc_wof_AUS_047</t>
   </si>
   <si>
-    <t>wind offshore electricity near Darwin (cluster 47)</t>
+    <t>wind offshore electricity near Hobart (cluster 47)</t>
   </si>
   <si>
     <t>elc_wof_AUS_048</t>
@@ -1659,7 +1659,7 @@
     <t>elc_wof_AUS_050</t>
   </si>
   <si>
-    <t>wind offshore electricity near Hobart (cluster 50)</t>
+    <t>wind offshore electricity near Darwin (cluster 50)</t>
   </si>
   <si>
     <t>elc_wof_AUS_051</t>
@@ -1779,19 +1779,19 @@
     <t>elc_won_AUS_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rockhampton (cluster 18)</t>
+    <t>wind onshore electricity near Brisbane (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_AUS_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bundaberg (cluster 19)</t>
+    <t>wind onshore electricity near Rockhampton (cluster 19)</t>
   </si>
   <si>
     <t>elc_won_AUS_020</t>
   </si>
   <si>
-    <t>wind onshore electricity near Townsville (cluster 20)</t>
+    <t>wind onshore electricity near Bundaberg (cluster 20)</t>
   </si>
   <si>
     <t>elc_won_AUS_021</t>
@@ -1803,19 +1803,19 @@
     <t>elc_won_AUS_022</t>
   </si>
   <si>
-    <t>wind onshore electricity near Canberra (cluster 22)</t>
+    <t>wind onshore electricity near Townsville (cluster 22)</t>
   </si>
   <si>
     <t>elc_won_AUS_023</t>
   </si>
   <si>
-    <t>wind onshore electricity near Adelaide (cluster 23)</t>
+    <t>wind onshore electricity near Canberra (cluster 23)</t>
   </si>
   <si>
     <t>elc_won_AUS_024</t>
   </si>
   <si>
-    <t>wind onshore electricity near Brisbane (cluster 24)</t>
+    <t>wind onshore electricity near Adelaide (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_AUS_025</t>
@@ -2175,7 +2175,7 @@
     <t>elc_won_AUS_084</t>
   </si>
   <si>
-    <t>wind onshore electricity near Darwin (cluster 84)</t>
+    <t>wind onshore electricity near Hobart (cluster 84)</t>
   </si>
   <si>
     <t>elc_won_AUS_085</t>
@@ -2205,7 +2205,7 @@
     <t>elc_won_AUS_089</t>
   </si>
   <si>
-    <t>wind onshore electricity near Hobart (cluster 89)</t>
+    <t>wind onshore electricity near Darwin (cluster 89)</t>
   </si>
   <si>
     <t>elc_won_AUS_090</t>
@@ -2298,12 +2298,6 @@
     <t>grid node -- way/171486427-275 (Rockhampton, 18 km)</t>
   </si>
   <si>
-    <t>e_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>grid node -- way/172587651-275 (Brisbane, 30 km)</t>
-  </si>
-  <si>
     <t>e_Broadsound_AUS</t>
   </si>
   <si>
@@ -2376,18 +2370,18 @@
     <t>grid node -- way/480009927-500 (Cranbourne, 102 km)</t>
   </si>
   <si>
-    <t>e_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>grid node -- AU146-220 (Hobart, 50 km)</t>
-  </si>
-  <si>
     <t>e_Horsham_AUS</t>
   </si>
   <si>
     <t>grid node -- AU104-220 (Ballarat, 167 km)</t>
   </si>
   <si>
+    <t>e_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>grid node -- way/170832455-275 (Brisbane, 25 km)</t>
+  </si>
+  <si>
     <t>e_Kalgoorlie_AUS</t>
   </si>
   <si>
@@ -2400,6 +2394,12 @@
     <t>grid node -- way/583492111-220 (Perth, 1248 km)</t>
   </si>
   <si>
+    <t>e_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>grid node -- AU147-220 (Hobart, 11 km)</t>
+  </si>
+  <si>
     <t>e_Merredin_AUS</t>
   </si>
   <si>
@@ -2574,12 +2574,6 @@
     <t>heat at grid node -- way/171486427-275 (Rockhampton, 18 km)</t>
   </si>
   <si>
-    <t>h_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/172587651-275 (Brisbane, 30 km)</t>
-  </si>
-  <si>
     <t>h_Broadsound_AUS</t>
   </si>
   <si>
@@ -2652,18 +2646,18 @@
     <t>heat at grid node -- way/480009927-500 (Cranbourne, 102 km)</t>
   </si>
   <si>
-    <t>h_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>heat at grid node -- AU146-220 (Hobart, 50 km)</t>
-  </si>
-  <si>
     <t>h_Horsham_AUS</t>
   </si>
   <si>
     <t>heat at grid node -- AU104-220 (Ballarat, 167 km)</t>
   </si>
   <si>
+    <t>h_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170832455-275 (Brisbane, 25 km)</t>
+  </si>
+  <si>
     <t>h_Kalgoorlie_AUS</t>
   </si>
   <si>
@@ -2674,6 +2668,12 @@
   </si>
   <si>
     <t>heat at grid node -- way/583492111-220 (Perth, 1248 km)</t>
+  </si>
+  <si>
+    <t>h_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>heat at grid node -- AU147-220 (Hobart, 11 km)</t>
   </si>
   <si>
     <t>h_Merredin_AUS</t>
@@ -5206,7 +5206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AAF3913-2173-4E01-ACB1-9AD0E2C5F306}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E50C04B5-C717-445C-8628-AAA458E9302D}">
   <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6443,7 +6443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1809D02-F27F-47CE-9096-5E1B2FAA398C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E0FCBF6-26AD-45AB-AA0E-14CDD0C0A7BD}">
   <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443156C0-0EAE-4EB1-8221-059840C79F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8349E270-04A3-40EB-B203-1AE0B1EF1601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5206,7 +5206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E50C04B5-C717-445C-8628-AAA458E9302D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBE4CD88-FF37-47AE-84D9-B75149D97E3A}">
   <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6443,7 +6443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E0FCBF6-26AD-45AB-AA0E-14CDD0C0A7BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CB78FB-64F2-4BAA-8BC5-95929660C908}">
   <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8349E270-04A3-40EB-B203-1AE0B1EF1601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5735F79-B967-40FB-A3EE-557211F47858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5206,7 +5206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBE4CD88-FF37-47AE-84D9-B75149D97E3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41E2E56-859D-44A9-A471-2A42AA7D3412}">
   <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6443,7 +6443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CB78FB-64F2-4BAA-8BC5-95929660C908}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F440907-5D0E-46BB-8411-F00986E1ECB5}">
   <dimension ref="B3:I50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
